--- a/EXCEL/SILENT_Settings_Datatable.xlsx
+++ b/EXCEL/SILENT_Settings_Datatable.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="140" customWidth="1" style="10" min="1" max="1"/>
@@ -554,7 +554,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>파일 6개, 시트 23개. 시트 하나 = CSV 하나(시트 이름.csv, UTF-8). _README · _COLUMNS 시트는 설명용이라 내보내지 않습니다.</t>
+          <t>파일 6개, 시트 16개. 시트 하나 = CSV 하나(시트 이름.csv, UTF-8). _README · _COLUMNS 시트는 설명용이라 내보내지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SILENT_Object_Datatable.xlsx: LOCK, CONSOLE, CARD, FRAME, ARROW, WIRE, FORMULA, PAPER, TV</t>
+          <t>SILENT_Object_Datatable.xlsx: LOCK, CONSOLE</t>
         </is>
       </c>
     </row>
@@ -651,184 +651,164 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  │    └ CARD · FRAME · ARROW · WIRE · FORMULA · PAPER · TV (앵커의 값, AnchorRef)</t>
+          <t xml:space="preserve">  └ PUZZLE (퍼즐, SolverRoom · ClueRoom, 입력 장치 InputAnchor)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ PUZZLE (퍼즐, SolverRoom · ClueRoom, 입력 장치 InputAnchor)</t>
+          <t xml:space="preserve">       ├ PUZZLE_SLOT (정답 칸, PuzzleID)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">       ├ PUZZLE_SLOT (정답 칸, PuzzleID)</t>
+          <t xml:space="preserve">       └ COLOR_LETTER (풀리면 보여 줄 색 글자, PuzzleID, 표시판 SignAnchor)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └ COLOR_LETTER (풀리면 보여 줄 색 글자, PuzzleID, 표시판 SignAnchor)</t>
+          <t>라이브러리: PREFAB ← COMPONENT (Components), SOUND ← SOUND_LINK (SoundID), GAME_CONFIG → CHARACTER_STAT (16010)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>라이브러리: PREFAB ← COMPONENT (Components), SOUND ← SOUND_LINK (SoundID), GAME_CONFIG → CHARACTER_STAT (16010)</t>
+          <t>전체 시트 목록, 부모, 읽는 순서: Settings 파일의 REGISTRY</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>전체 시트 목록, 부모, 읽는 순서: Settings 파일의 REGISTRY</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>공통 규칙</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>공통 규칙</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>1~4행: 1행 그 시트만의 규칙, 2행 기능, 3행 역할, 4행 의도. 5행 열 이름, 6행부터 데이터. CSV 리더는 앞 4줄을 건너뜀</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1~4행: 1행 그 시트만의 규칙, 2행 기능, 3행 역할, 4행 의도. 5행 열 이름, 6행부터 데이터. CSV 리더는 앞 4줄을 건너뜀</t>
+          <t>1열 ID: 숫자, 시트 구간 안에서 차례로. 지운 번호는 다시 쓰지 않음. Object 파일 시트의 1열 AnchorRef는 새 번호가 아니라 앵커 ID(두 앵커 시트가 2001~ 구간을 함께 써서 번호가 겹치지 않음.)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="27.75" customHeight="1" s="10">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1열 ID: 숫자, 시트 구간 안에서 차례로. 지운 번호는 다시 쓰지 않음. Object 파일 시트의 1열 AnchorRef는 새 번호가 아니라 앵커 ID(두 앵커 시트가 2001~ 구간을 함께 써서 번호가 겹치지 않음. 카드는 여러 장이 한 앵커라 CARD만 자기 ID 3001~)</t>
+          <t>2열 Name: 한국어 설명. 겹쳐도 되고 코드가 읽지 않음. 겹치면 안 되는 문자열은 두 앵커 시트의 AnchorID(Unity 앵커 이름) 하나</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2열 Name: 한국어 설명. 겹쳐도 되고 코드가 읽지 않음. 겹치면 안 되는 문자열은 두 앵커 시트의 AnchorID(Unity 앵커 이름) 하나</t>
+          <t>참조: 다른 시트는 숫자 ID로만 가리킴. 여러 개면 | 로 구분</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>참조: 다른 시트는 숫자 ID로만 가리킴. 여러 개면 | 로 구분</t>
+          <t>코드가 읽는 단어 값(색, 방향, 기호, 유형)은 아래 정해진 영어 단어로 씀</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>코드가 읽는 단어 값(색, 방향, 기호, 유형)은 아래 정해진 영어 단어로 씀</t>
+          <t>Active = N인 행은 읽지 않음. 단위: 거리 m, 시간 ms(밀리초, 1000 = 1초, 정수). 좌표는 DataTable에 없음(앵커 자리는 Unity 방 프리팹에서 정함)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Active = N인 행은 읽지 않음. 단위: 거리 m, 시간 ms(밀리초, 1000 = 1초, 정수). 좌표는 DataTable에 없음(앵커 자리는 Unity 방 프리팹에서 정함)</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>정해진 단어</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>정해진 단어</t>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Colour: Red, Green, Blue, Gray, Black, Orange, Yellow, SkyBlue, Pink, Purple, Crimson, White, Teal, Navy (글자 색 6개의 코드는 아트 01)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Colour: Red, Green, Blue, Gray, Black, Orange, Yellow, SkyBlue, Pink, Purple, Crimson, White, Teal, Navy (글자 색 6개의 코드는 아트 01)</t>
+          <t>Symbol: BlackDiamond ◆, WhiteDiamond ◇, BlackSpade ♠, WhiteSpade ♤, BlackHeart ♥, WhiteHeart ♡, Star ★, Heart (빨간 하트 그림), Spade (검은 스페이드 그림), None</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Symbol: BlackDiamond ◆, WhiteDiamond ◇, BlackSpade ♠, WhiteSpade ♤, BlackHeart ♥, WhiteHeart ♡, Star ★, Heart (빨간 하트 그림), Spade (검은 스페이드 그림), None</t>
+          <t>Direction: Up, Down, Left, Right / Wall: North, South</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Direction: Up, Down, Left, Right / Wall: North, South</t>
+          <t>Role: Solver, Clue / ExitRule: SolvedEach, BothSolved</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Role: Solver, Clue / ExitRule: SolvedEach, BothSolved</t>
+          <t>Type (PUZZLE): CardLetter, FrameCount, ArrowSequence, WireRank, TwistedFormula, TVLetter, ColourWord</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Type (PUZZLE): CardLetter, FrameCount, ArrowSequence, WireRank, TwistedFormula, TVLetter, ColourWord</t>
+          <t>DialFace (LOCK): Number1_9, Number0_9, Letter9, Color6 / DisplayFace: Letter, Color, Number, LetterWindow</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>DecoyType (CARD): None, LetterLetter, NumberNumber, SymbolZero, SymbolOne, SymbolTwo, SymbolThree, SymbolFour, IconIcon</t>
+          <t>Trigger (SOUND_LINK): OnStep, OnInteract, OnCloseUpOpen, OnCloseUpClose, OnDialTurn, OnConfirm, OnButton, OnClear, OnSpawn, OnDoorOpen, OnDoorLocked, OnSolved, OnLetterShow, OnWrong, OnInputUnlock, OnRoomEnter, OnRadioRxStart, OnRadioRxEnd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Category (FORMULA): Definition, Basic, Linear, Quadratic, Cubic, School, Discrete</t>
+          <t>Category (SOUND): Footstep, Interact, ObjectLoop, Door, PuzzleSolved, PuzzleWrong, Ambient, Radio / Space: 2D, 3D / Bus: SFX, Ambient, UI, Radio</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>DialFace (LOCK): Number1_9, Number0_9, Letter9, Color6 / DisplayFace: Letter, Color, Number, LetterWindow</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="27.75" customHeight="1" s="10">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Trigger (SOUND_LINK): OnStep, OnInteract, OnCloseUpOpen, OnCloseUpClose, OnDialTurn, OnConfirm, OnButton, OnClear, OnSpawn, OnDoorOpen, OnDoorLocked, OnSolved, OnLetterShow, OnWrong, OnInputUnlock, OnRoomEnter, OnRadioRxStart, OnRadioRxEnd</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Category (SOUND): Footstep, Interact, ObjectLoop, Door, PuzzleSolved, PuzzleWrong, Ambient, Radio / Space: 2D, 3D / Bus: SFX, Ambient, UI, Radio</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Y / N: Active, IsAnswer (정답에 쓰이는 것 = Y: CARD, FRAME, ARROW, WIRE, FORMULA, PAPER, TV), Flip, Loop, Required</t>
-        </is>
-      </c>
-    </row>
+          <t>Y / N: Active, Flip, Loop, Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="27.75" customHeight="1" s="10"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1586,7 +1566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="10" customWidth="1" style="10" min="1" max="1"/>
@@ -1689,95 +1669,97 @@
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
-        <v>16001</v>
+        <v>16010</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>목표 시간</t>
+          <t>쓰는 캐릭터 프로필</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>900000</v>
+        <v>17001</v>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+      <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>15분</t>
+          <t>CHARACTER_STAT ID</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>16002</v>
+        <v>16011</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>타이머 기본 색</t>
+          <t>엔딩 영상</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Video/Ending_SILENT.mp4</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>color</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="n"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>path</t>
+        </is>
+      </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>시작부터 14:00까지, 15:00 뒤 다시 이 색</t>
+          <t>약 20초</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
-        <v>16003</v>
+        <v>16030</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>타이머 경고 색</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
+          <t>발소리 간격</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>0.75</v>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>color</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="n"/>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>16012부터 16001까지</t>
+          <t>이만큼 걸을 때마다 발소리 한 번</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>16004</v>
+        <v>16031</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>오답 입력 잠금</t>
+          <t>배경음 전환 시간</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>5000</v>
+        <v>1500</v>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
@@ -1791,381 +1773,29 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>오답 뒤 확인 버튼이 막히는 시간. PUZZLE.WrongLockMs가 비면 이 값</t>
+          <t>방 배경음이 바뀔 때 겹치는 시간</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
-        <v>16005</v>
+        <v>16032</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>결과 조회 간격</t>
+          <t>대화 중 볼륨 배율</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1000</v>
+        <v>0.6</v>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>클라이언트가 서버에 상태를 묻는 간격</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>16006</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>이탈 판정 시간</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>이 시간 동안 요청이 없으면 이탈</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>16007</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>세션 내부 상한</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>끝나지 않는 세션 정리용, 화면에 안 보임</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>16010</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>쓰는 캐릭터 프로필</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>17001</v>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>CHARACTER_STAT ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>16011</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>엔딩 영상</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Video/Ending_SILENT.mp4</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>path</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>약 20초</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>16012</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>타이머 경고 시작</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>840000</v>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>14:00부터 빨강</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>16013</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>옵션 메뉴 키</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Escape</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>옵션 메뉴 열기 · 닫기</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n">
-        <v>16014</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>플레이어 이름 패널 위치</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>TopLeft</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>A 위, B 아래. 말하는 사람의 마이크 아이콘이 켜짐</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
-        <v>16019</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>3번 방 단서 표시</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>WhiteCircle</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>단서 화살표에 흰 동그라미, 안내 글 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="n">
-        <v>16020</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>4번 방 뚜껑 선 힌트</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>LongLeftShortRight</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>뚜껑의 선 표시, 왼쪽이 1위(가장 긴 전선) 쪽</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="n">
-        <v>16023</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>7번 방 대기 문구</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Waiting</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>먼저 푼 사람의 자물쇠 글자 창 아래에 상대가 풀 때까지 표시</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n">
-        <v>16030</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>발소리 간격</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>이만큼 걸을 때마다 발소리 한 번</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="n">
-        <v>16031</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>배경음 전환 시간</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>방 배경음이 바뀔 때 겹치는 시간</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="n">
-        <v>16032</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>대화 중 볼륨 배율</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>상대가 말하는 동안 Ambient · SFX 버스를 이 배율로 낮춤</t>
         </is>
@@ -2194,7 +1824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="10" customWidth="1" style="10" min="1" max="1"/>
@@ -2396,55 +2026,6 @@
       </c>
       <c r="O7" s="8" t="n">
         <v>0.02</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>17002</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>QA용 빠른 이동</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M8" s="8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="O8" s="8" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2470,7 +2051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="10" customWidth="1" style="10" min="1" max="1"/>
@@ -3187,45 +2768,45 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>18023</v>
+        <v>18009</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>카드 값</t>
+          <t>퍼즐</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>CARD</t>
+          <t>PUZZLE</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>SILENT_Object_Datatable.xlsx</t>
+          <t>SILENT_Puzzle_Datatable.xlsx</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>ANCHOR_NONINTERACT</t>
+          <t>ROOM_A, ROOM_B</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>AnchorRef</t>
+          <t>SolverRoom</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ANCHOR_INTERACT</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>3001~</t>
+          <t>5001~</t>
         </is>
       </c>
       <c r="I18" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
@@ -3240,31 +2821,31 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
-        <v>18024</v>
+        <v>18010</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>액자 값</t>
+          <t>정답 칸</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>FRAME</t>
+          <t>PUZZLE_SLOT</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>SILENT_Object_Datatable.xlsx</t>
+          <t>SILENT_Puzzle_Datatable.xlsx</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>ANCHOR_NONINTERACT</t>
+          <t>PUZZLE</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>AnchorRef</t>
+          <t>PuzzleID</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -3274,7 +2855,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>ANCHOR_NONINTERACT ID</t>
+          <t>6001~</t>
         </is>
       </c>
       <c r="I19" s="8" t="n">
@@ -3293,41 +2874,41 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>18025</v>
+        <v>18011</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>화살표 값</t>
+          <t>색 글자</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>ARROW</t>
+          <t>COLOR_LETTER</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>SILENT_Object_Datatable.xlsx</t>
+          <t>SILENT_Puzzle_Datatable.xlsx</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
+          <t>PUZZLE</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>PuzzleID</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
           <t>ANCHOR_NONINTERACT</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>AnchorRef</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>ANCHOR_NONINTERACT ID</t>
+          <t>7001~</t>
         </is>
       </c>
       <c r="I20" s="8" t="n">
@@ -3346,31 +2927,31 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>18026</v>
+        <v>18016</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>전선 값</t>
+          <t>소리</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>WIRE</t>
+          <t>SOUND</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>SILENT_Object_Datatable.xlsx</t>
+          <t>SILENT_Sound_Datatable.xlsx</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>ANCHOR_NONINTERACT</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>AnchorRef</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -3380,15 +2961,15 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>ANCHOR_NONINTERACT ID</t>
+          <t>15001~</t>
         </is>
       </c>
       <c r="I21" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
@@ -3399,423 +2980,52 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>18027</v>
+        <v>18017</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>공식판 값</t>
+          <t>소리 연결</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>FORMULA</t>
+          <t>SOUND_LINK</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>SILENT_Object_Datatable.xlsx</t>
+          <t>SILENT_Sound_Datatable.xlsx</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>ANCHOR_NONINTERACT</t>
+          <t>SOUND</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>AnchorRef</t>
+          <t>SoundID</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ROOM_A, ROOM_B, PREFAB, ANCHOR_INTERACT, ANCHOR_NONINTERACT, PUZZLE</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>ANCHOR_NONINTERACT ID</t>
+          <t>20001~</t>
         </is>
       </c>
       <c r="I22" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="n">
-        <v>18028</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>종이 값</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>PAPER</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>SILENT_Object_Datatable.xlsx</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>ANCHOR_NONINTERACT</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>AnchorRef</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>ANCHOR_NONINTERACT ID</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K23" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="n">
-        <v>18029</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>TV 값</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>TV</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>SILENT_Object_Datatable.xlsx</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>ANCHOR_NONINTERACT</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>AnchorRef</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>ANCHOR_NONINTERACT ID</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="n">
-        <v>18009</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>퍼즐</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>PUZZLE</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>SILENT_Puzzle_Datatable.xlsx</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>ROOM_A, ROOM_B</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>SolverRoom</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>ANCHOR_INTERACT</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>5001~</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J25" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K25" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="n">
-        <v>18010</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>정답 칸</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>PUZZLE_SLOT</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>SILENT_Puzzle_Datatable.xlsx</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>PUZZLE</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>PuzzleID</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>6001~</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J26" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="n">
-        <v>18011</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>색 글자</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>COLOR_LETTER</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>SILENT_Puzzle_Datatable.xlsx</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>PUZZLE</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>PuzzleID</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>ANCHOR_NONINTERACT</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>7001~</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J27" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="n">
-        <v>18016</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>소리</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>SOUND</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>SILENT_Sound_Datatable.xlsx</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>15001~</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K28" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="n">
-        <v>18017</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>소리 연결</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>SOUND_LINK</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>SILENT_Sound_Datatable.xlsx</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>SOUND</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>SoundID</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>ROOM_A, ROOM_B, PREFAB, ANCHOR_INTERACT, ANCHOR_NONINTERACT, PUZZLE</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>20001~</t>
-        </is>
-      </c>
-      <c r="I29" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J29" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K29" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>

--- a/EXCEL/SILENT_Settings_Datatable.xlsx
+++ b/EXCEL/SILENT_Settings_Datatable.xlsx
@@ -1702,7 +1702,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Video/Ending_SILENT.mp4</t>
+          <t>Assets/2.Model/EndingVideo/EndingVideo.mp4</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">

--- a/EXCEL/SILENT_Settings_Datatable.xlsx
+++ b/EXCEL/SILENT_Settings_Datatable.xlsx
@@ -2051,7 +2051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="10" customWidth="1" style="10" min="1" max="1"/>
@@ -2925,112 +2925,6 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="n">
-        <v>18016</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>소리</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>SOUND</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>SILENT_Sound_Datatable.xlsx</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>15001~</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n">
-        <v>18017</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>소리 연결</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>SOUND_LINK</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>SILENT_Sound_Datatable.xlsx</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>SOUND</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>SoundID</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>ROOM_A, ROOM_B, PREFAB, ANCHOR_INTERACT, ANCHOR_NONINTERACT, PUZZLE</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>20001~</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B1:K1"/>
